--- a/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0003T0006Z000C1N4_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0003T0006Z000C1N4_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>37.1935627644235</v>
+        <v>6.043953949218818</v>
       </c>
       <c r="D2" t="n">
-        <v>33.98621926806765</v>
+        <v>5.522760631060994</v>
       </c>
       <c r="E2" t="n">
-        <v>12.07543855837993</v>
+        <v>1.962258765736739</v>
       </c>
       <c r="F2" t="n">
-        <v>10.36177400503967</v>
+        <v>1.683788275818946</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>14.56021977856104</v>
+        <v>2.366035714016169</v>
       </c>
       <c r="D3" t="n">
-        <v>15.18095017728872</v>
+        <v>2.466904403809417</v>
       </c>
       <c r="E3" t="n">
-        <v>12.07543855837993</v>
+        <v>1.962258765736739</v>
       </c>
       <c r="F3" t="n">
-        <v>10.36177400503967</v>
+        <v>1.683788275818946</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>16.5</v>
+        <v>2.68125</v>
       </c>
       <c r="D4" t="n">
-        <v>19.22691372135126</v>
+        <v>3.124373479719579</v>
       </c>
       <c r="E4" t="n">
-        <v>12.07543855837993</v>
+        <v>1.962258765736739</v>
       </c>
       <c r="F4" t="n">
-        <v>10.36177400503967</v>
+        <v>1.683788275818946</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>27.55110210655716</v>
+        <v>4.477054092315539</v>
       </c>
       <c r="D5" t="n">
-        <v>27.5947504807644</v>
+        <v>4.484146953124214</v>
       </c>
       <c r="E5" t="n">
-        <v>12.07543855837993</v>
+        <v>1.962258765736739</v>
       </c>
       <c r="F5" t="n">
-        <v>10.36177400503967</v>
+        <v>1.683788275818946</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>48.54782560672225</v>
+        <v>7.889021661092365</v>
       </c>
       <c r="D6" t="n">
-        <v>48.54936786443359</v>
+        <v>7.889272277970459</v>
       </c>
       <c r="E6" t="n">
-        <v>12.07543855837993</v>
+        <v>1.962258765736739</v>
       </c>
       <c r="F6" t="n">
-        <v>10.36177400503967</v>
+        <v>1.683788275818946</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>44.19300040237466</v>
+        <v>7.181362565385883</v>
       </c>
       <c r="D7" t="n">
-        <v>41.4151647084569</v>
+        <v>6.729964265124246</v>
       </c>
       <c r="E7" t="n">
-        <v>12.07543855837993</v>
+        <v>1.962258765736739</v>
       </c>
       <c r="F7" t="n">
-        <v>10.36177400503967</v>
+        <v>1.683788275818946</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>40.44749683231337</v>
+        <v>6.572718235250923</v>
       </c>
       <c r="D8" t="n">
-        <v>27.96032176708289</v>
+        <v>4.54355228715097</v>
       </c>
       <c r="E8" t="n">
-        <v>12.07543855837993</v>
+        <v>1.962258765736739</v>
       </c>
       <c r="F8" t="n">
-        <v>10.36177400503967</v>
+        <v>1.683788275818946</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>42.573465914816</v>
+        <v>6.918188211157601</v>
       </c>
       <c r="D9" t="n">
-        <v>35.92937678550278</v>
+        <v>5.838523727644201</v>
       </c>
       <c r="E9" t="n">
-        <v>12.07543855837993</v>
+        <v>1.962258765736739</v>
       </c>
       <c r="F9" t="n">
-        <v>10.36177400503967</v>
+        <v>1.683788275818946</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
